--- a/src/test/resources/TestDriver/Hearst_POP/ActivityData/POP_AP.xlsx
+++ b/src/test/resources/TestDriver/Hearst_POP/ActivityData/POP_AP.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>standalone_price_policy</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>parent_child</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>parent_code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -458,6 +468,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,6 +493,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,6 +518,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,6 +543,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,6 +568,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -558,6 +593,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -578,6 +618,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_ALL_Recur_25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -598,6 +648,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_ALL_Recur_25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -618,6 +678,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -638,6 +703,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_ALL_Recur_4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -658,6 +733,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_ALL_Recur_4</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -678,6 +763,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -698,6 +788,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_New_2999</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -718,6 +818,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_New_2999</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -738,6 +848,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -758,6 +873,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_New_3499</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -778,6 +903,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_New_3499</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -798,6 +933,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -818,6 +958,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_New_42</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -838,6 +988,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_New_42</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -858,6 +1018,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -878,6 +1043,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_New_4499</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -898,6 +1073,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_New_4499</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -918,6 +1103,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -938,6 +1128,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_Renew_47</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -958,6 +1158,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_CAN_Renew_47</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -978,6 +1188,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -998,6 +1213,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_GIFT_US_3499</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1018,6 +1243,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_GIFT_US_3499</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1038,6 +1273,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1058,6 +1298,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_MGRT_CAN_Renew_47</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1078,6 +1328,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_MGRT_CAN_Renew_47</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1098,6 +1358,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1118,6 +1383,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_MGRT_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1138,6 +1413,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_MGRT_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1158,6 +1443,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1178,6 +1468,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1198,6 +1498,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_12</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1218,6 +1528,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1238,6 +1553,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_15</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1258,6 +1583,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_15</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1278,6 +1613,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1298,6 +1638,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_1999</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1318,6 +1668,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_1999</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1338,6 +1698,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1358,6 +1723,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_20</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1378,6 +1753,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_20</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1398,6 +1783,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1418,6 +1808,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_2499</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1438,6 +1838,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_2499</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1458,6 +1868,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1478,6 +1893,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_26</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1498,6 +1923,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_26</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1518,6 +1953,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1538,6 +1978,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1558,6 +2008,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_30</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1578,6 +2038,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1598,6 +2063,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_3499</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1618,6 +2093,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_3499</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1638,6 +2123,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1658,6 +2148,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1678,6 +2178,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_New_35</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1698,6 +2208,11 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1718,6 +2233,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1738,6 +2263,16 @@
           <t>DOLLAR_AMOUNT</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>POP_PRTDIG_US_Renew_40</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1758,6 +2293,11 @@
           <t>SALE_PRICE</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1776,6 +2316,11 @@
       <c r="D68" t="inlineStr">
         <is>
           <t>DOLLAR_AMOUNT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Parent</t>
         </is>
       </c>
     </row>
